--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1546"/>
+  <dimension ref="A1:I1547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42182,6 +42182,33 @@
       </c>
       <c r="I1546" t="inlineStr"/>
     </row>
+    <row r="1547">
+      <c r="A1547" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B1547" t="n">
+        <v>5128.7998046875</v>
+      </c>
+      <c r="C1547" t="n">
+        <v>5221.89990234375</v>
+      </c>
+      <c r="D1547" t="n">
+        <v>5120.39990234375</v>
+      </c>
+      <c r="E1547" t="n">
+        <v>5205.89990234375</v>
+      </c>
+      <c r="F1547" t="n">
+        <v>85864</v>
+      </c>
+      <c r="G1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1547" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1547"/>
+  <dimension ref="A1:I1548"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42209,6 +42209,33 @@
       </c>
       <c r="I1547" t="inlineStr"/>
     </row>
+    <row r="1548">
+      <c r="A1548" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B1548" t="n">
+        <v>5247.5</v>
+      </c>
+      <c r="C1548" t="n">
+        <v>5269.39990234375</v>
+      </c>
+      <c r="D1548" t="n">
+        <v>5109.5</v>
+      </c>
+      <c r="E1548" t="n">
+        <v>5157.7001953125</v>
+      </c>
+      <c r="F1548" t="n">
+        <v>104991</v>
+      </c>
+      <c r="G1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1548" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1548"/>
+  <dimension ref="A1:I1549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42236,6 +42236,33 @@
       </c>
       <c r="I1548" t="inlineStr"/>
     </row>
+    <row r="1549">
+      <c r="A1549" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B1549" t="n">
+        <v>5160</v>
+      </c>
+      <c r="C1549" t="n">
+        <v>5230</v>
+      </c>
+      <c r="D1549" t="n">
+        <v>5135.89990234375</v>
+      </c>
+      <c r="E1549" t="n">
+        <v>5208.5</v>
+      </c>
+      <c r="F1549" t="n">
+        <v>73336</v>
+      </c>
+      <c r="G1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1549" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1549"/>
+  <dimension ref="A1:I1550"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42263,6 +42263,33 @@
       </c>
       <c r="I1549" t="inlineStr"/>
     </row>
+    <row r="1550">
+      <c r="A1550" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B1550" t="n">
+        <v>5175.2998046875</v>
+      </c>
+      <c r="C1550" t="n">
+        <v>5221.89990234375</v>
+      </c>
+      <c r="D1550" t="n">
+        <v>5154.60009765625</v>
+      </c>
+      <c r="E1550" t="n">
+        <v>5181.2001953125</v>
+      </c>
+      <c r="F1550" t="n">
+        <v>73582</v>
+      </c>
+      <c r="G1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1550" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1550"/>
+  <dimension ref="A1:I1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42290,6 +42290,33 @@
       </c>
       <c r="I1550" t="inlineStr"/>
     </row>
+    <row r="1551">
+      <c r="A1551" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B1551" t="n">
+        <v>5201.89990234375</v>
+      </c>
+      <c r="C1551" t="n">
+        <v>5259.2998046875</v>
+      </c>
+      <c r="D1551" t="n">
+        <v>5182.89990234375</v>
+      </c>
+      <c r="E1551" t="n">
+        <v>5241.60009765625</v>
+      </c>
+      <c r="F1551" t="n">
+        <v>81147</v>
+      </c>
+      <c r="G1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1551" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -42298,16 +42298,16 @@
         <v>5201.89990234375</v>
       </c>
       <c r="C1551" t="n">
-        <v>5259.2998046875</v>
+        <v>5299</v>
       </c>
       <c r="D1551" t="n">
         <v>5182.89990234375</v>
       </c>
       <c r="E1551" t="n">
-        <v>5241.60009765625</v>
+        <v>5247.89990234375</v>
       </c>
       <c r="F1551" t="n">
-        <v>81147</v>
+        <v>145216</v>
       </c>
       <c r="G1551" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1551"/>
+  <dimension ref="A1:I1552"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42317,6 +42317,33 @@
       </c>
       <c r="I1551" t="inlineStr"/>
     </row>
+    <row r="1552">
+      <c r="A1552" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B1552" t="n">
+        <v>5360</v>
+      </c>
+      <c r="C1552" t="n">
+        <v>5434.10009765625</v>
+      </c>
+      <c r="D1552" t="n">
+        <v>5315.2998046875</v>
+      </c>
+      <c r="E1552" t="n">
+        <v>5346.5</v>
+      </c>
+      <c r="F1552" t="n">
+        <v>154408</v>
+      </c>
+      <c r="G1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1552" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1552"/>
+  <dimension ref="A1:I1553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42344,6 +42344,33 @@
       </c>
       <c r="I1552" t="inlineStr"/>
     </row>
+    <row r="1553">
+      <c r="A1553" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B1553" t="n">
+        <v>5335.7001953125</v>
+      </c>
+      <c r="C1553" t="n">
+        <v>5394.2001953125</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>5025</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>5058.39990234375</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>180302</v>
+      </c>
+      <c r="G1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1553" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1553"/>
+  <dimension ref="A1:I1554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42371,6 +42371,33 @@
       </c>
       <c r="I1553" t="inlineStr"/>
     </row>
+    <row r="1554">
+      <c r="A1554" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B1554" t="n">
+        <v>5110</v>
+      </c>
+      <c r="C1554" t="n">
+        <v>5218.2998046875</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>5092.7998046875</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>5165.2001953125</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>89263</v>
+      </c>
+      <c r="G1554" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1554" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1554" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1554"/>
+  <dimension ref="A1:I1555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42398,6 +42398,33 @@
       </c>
       <c r="I1554" t="inlineStr"/>
     </row>
+    <row r="1555">
+      <c r="A1555" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B1555" t="n">
+        <v>5155.7001953125</v>
+      </c>
+      <c r="C1555" t="n">
+        <v>5204.2998046875</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>5085.5</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>5125.5</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>88828</v>
+      </c>
+      <c r="G1555" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1555" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1555" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1555"/>
+  <dimension ref="A1:I1556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42425,6 +42425,33 @@
       </c>
       <c r="I1555" t="inlineStr"/>
     </row>
+    <row r="1556">
+      <c r="A1556" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B1556" t="n">
+        <v>5099.7001953125</v>
+      </c>
+      <c r="C1556" t="n">
+        <v>5151.2998046875</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>5071</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>5112.7001953125</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>82247</v>
+      </c>
+      <c r="G1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1556" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -42433,16 +42433,16 @@
         <v>5099.7001953125</v>
       </c>
       <c r="C1556" t="n">
-        <v>5151.2998046875</v>
+        <v>5185</v>
       </c>
       <c r="D1556" t="n">
         <v>5071</v>
       </c>
       <c r="E1556" t="n">
-        <v>5112.7001953125</v>
+        <v>5158.7001953125</v>
       </c>
       <c r="F1556" t="n">
-        <v>82247</v>
+        <v>148507</v>
       </c>
       <c r="G1556" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1556"/>
+  <dimension ref="A1:I1557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42452,6 +42452,33 @@
       </c>
       <c r="I1556" t="inlineStr"/>
     </row>
+    <row r="1557">
+      <c r="A1557" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B1557" t="n">
+        <v>5186.7001953125</v>
+      </c>
+      <c r="C1557" t="n">
+        <v>5210.39990234375</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>5021.2001953125</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>5096.60009765625</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>128486</v>
+      </c>
+      <c r="G1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1557" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1557"/>
+  <dimension ref="A1:I1558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42479,6 +42479,33 @@
       </c>
       <c r="I1557" t="inlineStr"/>
     </row>
+    <row r="1558">
+      <c r="A1558" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B1558" t="n">
+        <v>5152.39990234375</v>
+      </c>
+      <c r="C1558" t="n">
+        <v>5238.89990234375</v>
+      </c>
+      <c r="D1558" t="n">
+        <v>5127.10009765625</v>
+      </c>
+      <c r="E1558" t="n">
+        <v>5235.2001953125</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>111346</v>
+      </c>
+      <c r="G1558" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1558" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1558" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1558"/>
+  <dimension ref="A1:I1559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42506,6 +42506,33 @@
       </c>
       <c r="I1558" t="inlineStr"/>
     </row>
+    <row r="1559">
+      <c r="A1559" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B1559" t="n">
+        <v>5194</v>
+      </c>
+      <c r="C1559" t="n">
+        <v>5230.89990234375</v>
+      </c>
+      <c r="D1559" t="n">
+        <v>5155.89990234375</v>
+      </c>
+      <c r="E1559" t="n">
+        <v>5188.7001953125</v>
+      </c>
+      <c r="F1559" t="n">
+        <v>86423</v>
+      </c>
+      <c r="G1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1559" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1559"/>
+  <dimension ref="A1:I1560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42533,6 +42533,33 @@
       </c>
       <c r="I1559" t="inlineStr"/>
     </row>
+    <row r="1560">
+      <c r="A1560" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B1560" t="n">
+        <v>5185.39990234375</v>
+      </c>
+      <c r="C1560" t="n">
+        <v>5197.7998046875</v>
+      </c>
+      <c r="D1560" t="n">
+        <v>5114.60009765625</v>
+      </c>
+      <c r="E1560" t="n">
+        <v>5132.60009765625</v>
+      </c>
+      <c r="F1560" t="n">
+        <v>90002</v>
+      </c>
+      <c r="G1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1560" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1560"/>
+  <dimension ref="A1:I1561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42560,6 +42560,33 @@
       </c>
       <c r="I1560" t="inlineStr"/>
     </row>
+    <row r="1561">
+      <c r="A1561" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B1561" t="n">
+        <v>5084</v>
+      </c>
+      <c r="C1561" t="n">
+        <v>5132.39990234375</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>5039.2998046875</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>5052</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>92540</v>
+      </c>
+      <c r="G1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1561" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -42571,13 +42571,13 @@
         <v>5132.39990234375</v>
       </c>
       <c r="D1561" t="n">
-        <v>5039.2998046875</v>
+        <v>5014.10009765625</v>
       </c>
       <c r="E1561" t="n">
-        <v>5052</v>
+        <v>5061.7001953125</v>
       </c>
       <c r="F1561" t="n">
-        <v>92540</v>
+        <v>155259</v>
       </c>
       <c r="G1561" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1561"/>
+  <dimension ref="A1:I1562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42587,6 +42587,33 @@
       </c>
       <c r="I1561" t="inlineStr"/>
     </row>
+    <row r="1562">
+      <c r="A1562" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B1562" t="n">
+        <v>5010</v>
+      </c>
+      <c r="C1562" t="n">
+        <v>5044.5</v>
+      </c>
+      <c r="D1562" t="n">
+        <v>4970.10009765625</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>4994.60009765625</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>130118</v>
+      </c>
+      <c r="G1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1562" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1562"/>
+  <dimension ref="A1:I1563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42614,6 +42614,33 @@
       </c>
       <c r="I1562" t="inlineStr"/>
     </row>
+    <row r="1563">
+      <c r="A1563" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B1563" t="n">
+        <v>5012.2001953125</v>
+      </c>
+      <c r="C1563" t="n">
+        <v>5049.39990234375</v>
+      </c>
+      <c r="D1563" t="n">
+        <v>4994.7998046875</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>5005.60009765625</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>82466</v>
+      </c>
+      <c r="G1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1563" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1563"/>
+  <dimension ref="A1:I1564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42641,6 +42641,33 @@
       </c>
       <c r="I1563" t="inlineStr"/>
     </row>
+    <row r="1564">
+      <c r="A1564" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B1564" t="n">
+        <v>5010.60009765625</v>
+      </c>
+      <c r="C1564" t="n">
+        <v>5022</v>
+      </c>
+      <c r="D1564" t="n">
+        <v>4837.10009765625</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>4877.10009765625</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>154776</v>
+      </c>
+      <c r="G1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1564" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1564"/>
+  <dimension ref="A1:I1565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42668,6 +42668,33 @@
       </c>
       <c r="I1564" t="inlineStr"/>
     </row>
+    <row r="1565">
+      <c r="A1565" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B1565" t="n">
+        <v>4828</v>
+      </c>
+      <c r="C1565" t="n">
+        <v>4868.7001953125</v>
+      </c>
+      <c r="D1565" t="n">
+        <v>4505</v>
+      </c>
+      <c r="E1565" t="n">
+        <v>4599.5</v>
+      </c>
+      <c r="F1565" t="n">
+        <v>225448</v>
+      </c>
+      <c r="G1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1565" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1565"/>
+  <dimension ref="A1:I1566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42695,6 +42695,33 @@
       </c>
       <c r="I1565" t="inlineStr"/>
     </row>
+    <row r="1566">
+      <c r="A1566" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B1566" t="n">
+        <v>4653.89990234375</v>
+      </c>
+      <c r="C1566" t="n">
+        <v>4738.2001953125</v>
+      </c>
+      <c r="D1566" t="n">
+        <v>4547.60009765625</v>
+      </c>
+      <c r="E1566" t="n">
+        <v>4571.60009765625</v>
+      </c>
+      <c r="F1566" t="n">
+        <v>144696</v>
+      </c>
+      <c r="G1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1566" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -42706,13 +42706,13 @@
         <v>4738.2001953125</v>
       </c>
       <c r="D1566" t="n">
-        <v>4547.60009765625</v>
+        <v>4478.39990234375</v>
       </c>
       <c r="E1566" t="n">
-        <v>4571.60009765625</v>
+        <v>4574.89990234375</v>
       </c>
       <c r="F1566" t="n">
-        <v>144696</v>
+        <v>220773</v>
       </c>
       <c r="G1566" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1566"/>
+  <dimension ref="A1:I1567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42722,6 +42722,33 @@
       </c>
       <c r="I1566" t="inlineStr"/>
     </row>
+    <row r="1567">
+      <c r="A1567" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B1567" t="n">
+        <v>4450</v>
+      </c>
+      <c r="C1567" t="n">
+        <v>4537.10009765625</v>
+      </c>
+      <c r="D1567" t="n">
+        <v>4100</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>4456.2998046875</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>325859</v>
+      </c>
+      <c r="G1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1567" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1567"/>
+  <dimension ref="A1:I1568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42749,6 +42749,33 @@
       </c>
       <c r="I1567" t="inlineStr"/>
     </row>
+    <row r="1568">
+      <c r="A1568" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B1568" t="n">
+        <v>4414.7998046875</v>
+      </c>
+      <c r="C1568" t="n">
+        <v>4450.5</v>
+      </c>
+      <c r="D1568" t="n">
+        <v>4306.2998046875</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>4414.2998046875</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>154995</v>
+      </c>
+      <c r="G1568" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1568" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1568" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1568"/>
+  <dimension ref="A1:I1569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42776,6 +42776,33 @@
       </c>
       <c r="I1568" t="inlineStr"/>
     </row>
+    <row r="1569">
+      <c r="A1569" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B1569" t="n">
+        <v>4473.5</v>
+      </c>
+      <c r="C1569" t="n">
+        <v>4601</v>
+      </c>
+      <c r="D1569" t="n">
+        <v>4458.2001953125</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>4562.60009765625</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>179605</v>
+      </c>
+      <c r="G1569" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1569" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1569" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1569"/>
+  <dimension ref="A1:I1570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42803,6 +42803,33 @@
       </c>
       <c r="I1569" t="inlineStr"/>
     </row>
+    <row r="1570">
+      <c r="A1570" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B1570" t="n">
+        <v>4508.89990234375</v>
+      </c>
+      <c r="C1570" t="n">
+        <v>4541.60009765625</v>
+      </c>
+      <c r="D1570" t="n">
+        <v>4409.2998046875</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>4435.39990234375</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>164427</v>
+      </c>
+      <c r="G1570" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1570" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1570" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1570"/>
+  <dimension ref="A1:I1571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42830,6 +42830,33 @@
       </c>
       <c r="I1570" t="inlineStr"/>
     </row>
+    <row r="1571">
+      <c r="A1571" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B1571" t="n">
+        <v>4371.7998046875</v>
+      </c>
+      <c r="C1571" t="n">
+        <v>4564.2001953125</v>
+      </c>
+      <c r="D1571" t="n">
+        <v>4400.60009765625</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>4555.60009765625</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>138657</v>
+      </c>
+      <c r="G1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1571" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -42838,16 +42838,16 @@
         <v>4371.7998046875</v>
       </c>
       <c r="C1571" t="n">
-        <v>4564.2001953125</v>
+        <v>4585.2998046875</v>
       </c>
       <c r="D1571" t="n">
         <v>4400.60009765625</v>
       </c>
       <c r="E1571" t="n">
-        <v>4555.60009765625</v>
+        <v>4524.2998046875</v>
       </c>
       <c r="F1571" t="n">
-        <v>138657</v>
+        <v>203551</v>
       </c>
       <c r="G1571" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1571"/>
+  <dimension ref="A1:I1572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42857,6 +42857,33 @@
       </c>
       <c r="I1571" t="inlineStr"/>
     </row>
+    <row r="1572">
+      <c r="A1572" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B1572" t="n">
+        <v>4520</v>
+      </c>
+      <c r="C1572" t="n">
+        <v>4611.39990234375</v>
+      </c>
+      <c r="D1572" t="n">
+        <v>4444.7001953125</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>4579.60009765625</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>123737</v>
+      </c>
+      <c r="G1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1572" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1572"/>
+  <dimension ref="A1:I1573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42884,6 +42884,33 @@
       </c>
       <c r="I1572" t="inlineStr"/>
     </row>
+    <row r="1573">
+      <c r="A1573" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B1573" t="n">
+        <v>4538.89990234375</v>
+      </c>
+      <c r="C1573" t="n">
+        <v>4662</v>
+      </c>
+      <c r="D1573" t="n">
+        <v>4510</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>4645.7998046875</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>124341</v>
+      </c>
+      <c r="G1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1573" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1573"/>
+  <dimension ref="A1:I1574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42911,6 +42911,33 @@
       </c>
       <c r="I1573" t="inlineStr"/>
     </row>
+    <row r="1574">
+      <c r="A1574" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B1574" t="n">
+        <v>4698.39990234375</v>
+      </c>
+      <c r="C1574" t="n">
+        <v>4811.2998046875</v>
+      </c>
+      <c r="D1574" t="n">
+        <v>4690</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>4808.89990234375</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>132661</v>
+      </c>
+      <c r="G1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1574" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1574"/>
+  <dimension ref="A1:I1575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42938,6 +42938,33 @@
       </c>
       <c r="I1574" t="inlineStr"/>
     </row>
+    <row r="1575">
+      <c r="A1575" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B1575" t="n">
+        <v>4783</v>
+      </c>
+      <c r="C1575" t="n">
+        <v>4825.89990234375</v>
+      </c>
+      <c r="D1575" t="n">
+        <v>4580.39990234375</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>4688.39990234375</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>158511</v>
+      </c>
+      <c r="G1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1575" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1575"/>
+  <dimension ref="A1:I1576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42965,6 +42965,33 @@
       </c>
       <c r="I1575" t="inlineStr"/>
     </row>
+    <row r="1576">
+      <c r="A1576" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B1576" t="n">
+        <v>4675</v>
+      </c>
+      <c r="C1576" t="n">
+        <v>4733.10009765625</v>
+      </c>
+      <c r="D1576" t="n">
+        <v>4626.2001953125</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>4701.60009765625</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>66352</v>
+      </c>
+      <c r="G1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1576" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1576"/>
+  <dimension ref="A1:I1577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42992,6 +42992,33 @@
       </c>
       <c r="I1576" t="inlineStr"/>
     </row>
+    <row r="1577">
+      <c r="A1577" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B1577" t="n">
+        <v>4678.60009765625</v>
+      </c>
+      <c r="C1577" t="n">
+        <v>4721.2001953125</v>
+      </c>
+      <c r="D1577" t="n">
+        <v>4631.89990234375</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>4673.5</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>106714</v>
+      </c>
+      <c r="G1577" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1577" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1577" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1577"/>
+  <dimension ref="A1:I1578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43019,6 +43019,33 @@
       </c>
       <c r="I1577" t="inlineStr"/>
     </row>
+    <row r="1578">
+      <c r="A1578" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B1578" t="n">
+        <v>4747.2001953125</v>
+      </c>
+      <c r="C1578" t="n">
+        <v>4888</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>4740.5</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>4780.39990234375</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>172427</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1578" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1578"/>
+  <dimension ref="A1:I1579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43046,6 +43046,33 @@
       </c>
       <c r="I1578" t="inlineStr"/>
     </row>
+    <row r="1579">
+      <c r="A1579" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B1579" t="n">
+        <v>4744.7998046875</v>
+      </c>
+      <c r="C1579" t="n">
+        <v>4823.89990234375</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>4718.60009765625</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>4809.7001953125</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>101518</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1579" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1579"/>
+  <dimension ref="A1:I1580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43073,6 +43073,33 @@
       </c>
       <c r="I1579" t="inlineStr"/>
     </row>
+    <row r="1580">
+      <c r="A1580" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B1580" t="n">
+        <v>4790.5</v>
+      </c>
+      <c r="C1580" t="n">
+        <v>4820</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>4752.7001953125</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>4801.5</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>83294</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1580" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -43087,10 +43087,10 @@
         <v>4752.7001953125</v>
       </c>
       <c r="E1580" t="n">
-        <v>4801.5</v>
+        <v>4787.39990234375</v>
       </c>
       <c r="F1580" t="n">
-        <v>83294</v>
+        <v>117744</v>
       </c>
       <c r="G1580" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1580"/>
+  <dimension ref="A1:I1581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43100,6 +43100,33 @@
       </c>
       <c r="I1580" t="inlineStr"/>
     </row>
+    <row r="1581">
+      <c r="A1581" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B1581" t="n">
+        <v>4710</v>
+      </c>
+      <c r="C1581" t="n">
+        <v>4768</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>4626</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>4733.2001953125</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>90039</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1581" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1581"/>
+  <dimension ref="A1:I1582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43127,6 +43127,33 @@
       </c>
       <c r="I1581" t="inlineStr"/>
     </row>
+    <row r="1582">
+      <c r="A1582" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B1582" t="n">
+        <v>4769.2998046875</v>
+      </c>
+      <c r="C1582" t="n">
+        <v>4842</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>4767.60009765625</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>4833.2001953125</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>92099</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1582" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1582" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1582"/>
+  <dimension ref="A1:I1583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43154,6 +43154,33 @@
       </c>
       <c r="I1582" t="inlineStr"/>
     </row>
+    <row r="1583">
+      <c r="A1583" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B1583" t="n">
+        <v>4862.7001953125</v>
+      </c>
+      <c r="C1583" t="n">
+        <v>4895.39990234375</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>4807.89990234375</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>4821.60009765625</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>81858</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1583" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1583"/>
+  <dimension ref="A1:I1584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43181,6 +43181,33 @@
       </c>
       <c r="I1583" t="inlineStr"/>
     </row>
+    <row r="1584">
+      <c r="A1584" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B1584" t="n">
+        <v>4813.60009765625</v>
+      </c>
+      <c r="C1584" t="n">
+        <v>4861.2998046875</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>4792.10009765625</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>4827.10009765625</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>88232</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1584" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1584"/>
+  <dimension ref="A1:I1585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43208,6 +43208,33 @@
       </c>
       <c r="I1584" t="inlineStr"/>
     </row>
+    <row r="1585">
+      <c r="A1585" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B1585" t="n">
+        <v>4811.7998046875</v>
+      </c>
+      <c r="C1585" t="n">
+        <v>4917.7001953125</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>4785.89990234375</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>4889.10009765625</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>105769</v>
+      </c>
+      <c r="G1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1585" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -43222,10 +43222,10 @@
         <v>4785.89990234375</v>
       </c>
       <c r="E1585" t="n">
-        <v>4889.10009765625</v>
+        <v>4879.60009765625</v>
       </c>
       <c r="F1585" t="n">
-        <v>105769</v>
+        <v>130225</v>
       </c>
       <c r="G1585" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1585"/>
+  <dimension ref="A1:I1586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43235,6 +43235,33 @@
       </c>
       <c r="I1585" t="inlineStr"/>
     </row>
+    <row r="1586">
+      <c r="A1586" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B1586" t="n">
+        <v>4811.7998046875</v>
+      </c>
+      <c r="C1586" t="n">
+        <v>4847.89990234375</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>4752</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>4822.60009765625</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>102885</v>
+      </c>
+      <c r="G1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1586" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1586"/>
+  <dimension ref="A1:I1587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43262,6 +43262,33 @@
       </c>
       <c r="I1586" t="inlineStr"/>
     </row>
+    <row r="1587">
+      <c r="A1587" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B1587" t="n">
+        <v>4842.39990234375</v>
+      </c>
+      <c r="C1587" t="n">
+        <v>4854.7998046875</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>4740.89990234375</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>4758.5</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>115281</v>
+      </c>
+      <c r="G1587" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1587" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1587" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1587"/>
+  <dimension ref="A1:I1588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43289,6 +43289,33 @@
       </c>
       <c r="I1587" t="inlineStr"/>
     </row>
+    <row r="1588">
+      <c r="A1588" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B1588" t="n">
+        <v>4738.7001953125</v>
+      </c>
+      <c r="C1588" t="n">
+        <v>4790.7998046875</v>
+      </c>
+      <c r="D1588" t="n">
+        <v>4733.10009765625</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>4745.5</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>78904</v>
+      </c>
+      <c r="G1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1588" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1588"/>
+  <dimension ref="A1:I1589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43316,6 +43316,33 @@
       </c>
       <c r="I1588" t="inlineStr"/>
     </row>
+    <row r="1589">
+      <c r="A1589" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B1589" t="n">
+        <v>4759.2001953125</v>
+      </c>
+      <c r="C1589" t="n">
+        <v>4771.2998046875</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>4700</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>4735.60009765625</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>108281</v>
+      </c>
+      <c r="G1589" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1589" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1589" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1589"/>
+  <dimension ref="A1:I1590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43343,6 +43343,33 @@
       </c>
       <c r="I1589" t="inlineStr"/>
     </row>
+    <row r="1590">
+      <c r="A1590" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B1590" t="n">
+        <v>4715.60009765625</v>
+      </c>
+      <c r="C1590" t="n">
+        <v>4757.10009765625</v>
+      </c>
+      <c r="D1590" t="n">
+        <v>4672.2001953125</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>4736.5</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>81700</v>
+      </c>
+      <c r="G1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1590" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -43357,10 +43357,10 @@
         <v>4672.2001953125</v>
       </c>
       <c r="E1590" t="n">
-        <v>4736.5</v>
+        <v>4740.89990234375</v>
       </c>
       <c r="F1590" t="n">
-        <v>81700</v>
+        <v>100809</v>
       </c>
       <c r="G1590" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1590"/>
+  <dimension ref="A1:I1591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43370,6 +43370,33 @@
       </c>
       <c r="I1590" t="inlineStr"/>
     </row>
+    <row r="1591">
+      <c r="A1591" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B1591" t="n">
+        <v>4713.10009765625</v>
+      </c>
+      <c r="C1591" t="n">
+        <v>4745.7998046875</v>
+      </c>
+      <c r="D1591" t="n">
+        <v>4681.7998046875</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>4684</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>67500</v>
+      </c>
+      <c r="G1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1591" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1591"/>
+  <dimension ref="A1:I1592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43397,6 +43397,33 @@
       </c>
       <c r="I1591" t="inlineStr"/>
     </row>
+    <row r="1592">
+      <c r="A1592" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B1592" t="n">
+        <v>4697.5</v>
+      </c>
+      <c r="C1592" t="n">
+        <v>4716.5</v>
+      </c>
+      <c r="D1592" t="n">
+        <v>4567.60009765625</v>
+      </c>
+      <c r="E1592" t="n">
+        <v>4597.5</v>
+      </c>
+      <c r="F1592" t="n">
+        <v>120930</v>
+      </c>
+      <c r="G1592" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1592" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1592" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1592"/>
+  <dimension ref="A1:I1593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43424,6 +43424,33 @@
       </c>
       <c r="I1592" t="inlineStr"/>
     </row>
+    <row r="1593">
+      <c r="A1593" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B1593" t="n">
+        <v>4611.39990234375</v>
+      </c>
+      <c r="C1593" t="n">
+        <v>4624.2998046875</v>
+      </c>
+      <c r="D1593" t="n">
+        <v>4522.2001953125</v>
+      </c>
+      <c r="E1593" t="n">
+        <v>4571.7001953125</v>
+      </c>
+      <c r="F1593" t="n">
+        <v>91910</v>
+      </c>
+      <c r="G1593" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1593" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1593" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1593"/>
+  <dimension ref="A1:I1594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43451,6 +43451,33 @@
       </c>
       <c r="I1593" t="inlineStr"/>
     </row>
+    <row r="1594">
+      <c r="A1594" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B1594" t="n">
+        <v>4557</v>
+      </c>
+      <c r="C1594" t="n">
+        <v>4658.7998046875</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>4550.7998046875</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>4627.2998046875</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>93447</v>
+      </c>
+      <c r="G1594" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1594" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1594" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1594"/>
+  <dimension ref="A1:I1595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43478,6 +43478,33 @@
       </c>
       <c r="I1594" t="inlineStr"/>
     </row>
+    <row r="1595">
+      <c r="A1595" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B1595" t="n">
+        <v>4636.89990234375</v>
+      </c>
+      <c r="C1595" t="n">
+        <v>4673</v>
+      </c>
+      <c r="D1595" t="n">
+        <v>4570</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>4648.5</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>69380</v>
+      </c>
+      <c r="G1595" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1595" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1595" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -43492,10 +43492,10 @@
         <v>4570</v>
       </c>
       <c r="E1595" t="n">
-        <v>4648.5</v>
+        <v>4644.5</v>
       </c>
       <c r="F1595" t="n">
-        <v>69380</v>
+        <v>91619</v>
       </c>
       <c r="G1595" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1595"/>
+  <dimension ref="A1:I1596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43505,6 +43505,33 @@
       </c>
       <c r="I1595" t="inlineStr"/>
     </row>
+    <row r="1596">
+      <c r="A1596" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B1596" t="n">
+        <v>4644</v>
+      </c>
+      <c r="C1596" t="n">
+        <v>4650.60009765625</v>
+      </c>
+      <c r="D1596" t="n">
+        <v>4520.60009765625</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>4525.60009765625</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>86062</v>
+      </c>
+      <c r="G1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1596" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1596"/>
+  <dimension ref="A1:I1597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43532,6 +43532,33 @@
       </c>
       <c r="I1596" t="inlineStr"/>
     </row>
+    <row r="1597">
+      <c r="A1597" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B1597" t="n">
+        <v>4569.2998046875</v>
+      </c>
+      <c r="C1597" t="n">
+        <v>4734.60009765625</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>4556.10009765625</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>4697.39990234375</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>134979</v>
+      </c>
+      <c r="G1597" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1597" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1597" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1597"/>
+  <dimension ref="A1:I1598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43559,6 +43559,33 @@
       </c>
       <c r="I1597" t="inlineStr"/>
     </row>
+    <row r="1598">
+      <c r="A1598" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B1598" t="n">
+        <v>4702.2001953125</v>
+      </c>
+      <c r="C1598" t="n">
+        <v>4775.2001953125</v>
+      </c>
+      <c r="D1598" t="n">
+        <v>4694</v>
+      </c>
+      <c r="E1598" t="n">
+        <v>4726.10009765625</v>
+      </c>
+      <c r="F1598" t="n">
+        <v>103020</v>
+      </c>
+      <c r="G1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1598" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1598"/>
+  <dimension ref="A1:I1599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43586,6 +43586,33 @@
       </c>
       <c r="I1598" t="inlineStr"/>
     </row>
+    <row r="1599">
+      <c r="A1599" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B1599" t="n">
+        <v>4682.5</v>
+      </c>
+      <c r="C1599" t="n">
+        <v>4760.39990234375</v>
+      </c>
+      <c r="D1599" t="n">
+        <v>4671</v>
+      </c>
+      <c r="E1599" t="n">
+        <v>4718.39990234375</v>
+      </c>
+      <c r="F1599" t="n">
+        <v>91473</v>
+      </c>
+      <c r="G1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1599" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -43600,10 +43600,10 @@
         <v>4671</v>
       </c>
       <c r="E1599" t="n">
-        <v>4718.39990234375</v>
+        <v>4730.7001953125</v>
       </c>
       <c r="F1599" t="n">
-        <v>91473</v>
+        <v>114845</v>
       </c>
       <c r="G1599" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1599"/>
+  <dimension ref="A1:I1600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43613,6 +43613,33 @@
       </c>
       <c r="I1599" t="inlineStr"/>
     </row>
+    <row r="1600">
+      <c r="A1600" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B1600" t="n">
+        <v>4690</v>
+      </c>
+      <c r="C1600" t="n">
+        <v>4758.39990234375</v>
+      </c>
+      <c r="D1600" t="n">
+        <v>4655.10009765625</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>4725.89990234375</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>117360</v>
+      </c>
+      <c r="G1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1600" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1600"/>
+  <dimension ref="A1:I1601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43640,6 +43640,33 @@
       </c>
       <c r="I1600" t="inlineStr"/>
     </row>
+    <row r="1601">
+      <c r="A1601" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B1601" t="n">
+        <v>4745.2998046875</v>
+      </c>
+      <c r="C1601" t="n">
+        <v>4783.39990234375</v>
+      </c>
+      <c r="D1601" t="n">
+        <v>4645.2001953125</v>
+      </c>
+      <c r="E1601" t="n">
+        <v>4675.7998046875</v>
+      </c>
+      <c r="F1601" t="n">
+        <v>113618</v>
+      </c>
+      <c r="G1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1601" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1601"/>
+  <dimension ref="A1:I1602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43667,6 +43667,33 @@
       </c>
       <c r="I1601" t="inlineStr"/>
     </row>
+    <row r="1602">
+      <c r="A1602" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B1602" t="n">
+        <v>4722.2998046875</v>
+      </c>
+      <c r="C1602" t="n">
+        <v>4734.7998046875</v>
+      </c>
+      <c r="D1602" t="n">
+        <v>4676</v>
+      </c>
+      <c r="E1602" t="n">
+        <v>4716.2001953125</v>
+      </c>
+      <c r="F1602" t="n">
+        <v>89765</v>
+      </c>
+      <c r="G1602" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1602" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1602" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1602"/>
+  <dimension ref="A1:I1603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43694,6 +43694,33 @@
       </c>
       <c r="I1602" t="inlineStr"/>
     </row>
+    <row r="1603">
+      <c r="A1603" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B1603" t="n">
+        <v>4696.7998046875</v>
+      </c>
+      <c r="C1603" t="n">
+        <v>4725.7998046875</v>
+      </c>
+      <c r="D1603" t="n">
+        <v>4671.2998046875</v>
+      </c>
+      <c r="E1603" t="n">
+        <v>4685.7001953125</v>
+      </c>
+      <c r="F1603" t="n">
+        <v>78558</v>
+      </c>
+      <c r="G1603" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1603" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1603" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1603"/>
+  <dimension ref="A1:I1604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43721,6 +43721,33 @@
       </c>
       <c r="I1603" t="inlineStr"/>
     </row>
+    <row r="1604">
+      <c r="A1604" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B1604" t="n">
+        <v>4654.5</v>
+      </c>
+      <c r="C1604" t="n">
+        <v>4670.10009765625</v>
+      </c>
+      <c r="D1604" t="n">
+        <v>4513.7998046875</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>4534.60009765625</v>
+      </c>
+      <c r="F1604" t="n">
+        <v>140696</v>
+      </c>
+      <c r="G1604" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1604" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1604" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -43735,10 +43735,10 @@
         <v>4513.7998046875</v>
       </c>
       <c r="E1604" t="n">
-        <v>4534.60009765625</v>
+        <v>4561.89990234375</v>
       </c>
       <c r="F1604" t="n">
-        <v>140696</v>
+        <v>161086</v>
       </c>
       <c r="G1604" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1604"/>
+  <dimension ref="A1:I1605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43748,6 +43748,33 @@
       </c>
       <c r="I1604" t="inlineStr"/>
     </row>
+    <row r="1605">
+      <c r="A1605" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B1605" t="n">
+        <v>4547.60009765625</v>
+      </c>
+      <c r="C1605" t="n">
+        <v>4588.60009765625</v>
+      </c>
+      <c r="D1605" t="n">
+        <v>4483.5</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>4561.89990234375</v>
+      </c>
+      <c r="F1605" t="n">
+        <v>133741</v>
+      </c>
+      <c r="G1605" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1605" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1605" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1605"/>
+  <dimension ref="A1:I1606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43775,6 +43775,33 @@
       </c>
       <c r="I1605" t="inlineStr"/>
     </row>
+    <row r="1606">
+      <c r="A1606" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B1606" t="n">
+        <v>4570.60009765625</v>
+      </c>
+      <c r="C1606" t="n">
+        <v>4593.2001953125</v>
+      </c>
+      <c r="D1606" t="n">
+        <v>4467.10009765625</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>4513.5</v>
+      </c>
+      <c r="F1606" t="n">
+        <v>124021</v>
+      </c>
+      <c r="G1606" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1606" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1606" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1606"/>
+  <dimension ref="A1:I1607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43802,6 +43802,33 @@
       </c>
       <c r="I1606" t="inlineStr"/>
     </row>
+    <row r="1607">
+      <c r="A1607" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B1607" t="n">
+        <v>4486.60009765625</v>
+      </c>
+      <c r="C1607" t="n">
+        <v>4558.39990234375</v>
+      </c>
+      <c r="D1607" t="n">
+        <v>4455</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>4535.5</v>
+      </c>
+      <c r="F1607" t="n">
+        <v>136173</v>
+      </c>
+      <c r="G1607" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1607" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1607" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1607"/>
+  <dimension ref="A1:I1608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43829,6 +43829,33 @@
       </c>
       <c r="I1607" t="inlineStr"/>
     </row>
+    <row r="1608">
+      <c r="A1608" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B1608" t="n">
+        <v>4548</v>
+      </c>
+      <c r="C1608" t="n">
+        <v>4572.39990234375</v>
+      </c>
+      <c r="D1608" t="n">
+        <v>4488.2998046875</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>4519.60009765625</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>120600</v>
+      </c>
+      <c r="G1608" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1608" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1608" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1608"/>
+  <dimension ref="A1:I1609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43856,6 +43856,33 @@
       </c>
       <c r="I1608" t="inlineStr"/>
     </row>
+    <row r="1609">
+      <c r="A1609" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B1609" t="n">
+        <v>4544.2001953125</v>
+      </c>
+      <c r="C1609" t="n">
+        <v>4547</v>
+      </c>
+      <c r="D1609" t="n">
+        <v>4488</v>
+      </c>
+      <c r="E1609" t="n">
+        <v>4527.2001953125</v>
+      </c>
+      <c r="F1609" t="n">
+        <v>87534</v>
+      </c>
+      <c r="G1609" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1609" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1609" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -43870,10 +43870,10 @@
         <v>4488</v>
       </c>
       <c r="E1609" t="n">
-        <v>4527.2001953125</v>
+        <v>4523.2001953125</v>
       </c>
       <c r="F1609" t="n">
-        <v>87534</v>
+        <v>106230</v>
       </c>
       <c r="G1609" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1609"/>
+  <dimension ref="A1:I1610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43883,6 +43883,33 @@
       </c>
       <c r="I1609" t="inlineStr"/>
     </row>
+    <row r="1610">
+      <c r="A1610" s="1" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B1610" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C1610" t="n">
+        <v>4582.60009765625</v>
+      </c>
+      <c r="D1610" t="n">
+        <v>4531.2998046875</v>
+      </c>
+      <c r="E1610" t="n">
+        <v>4523.2001953125</v>
+      </c>
+      <c r="F1610" t="n">
+        <v>60056</v>
+      </c>
+      <c r="G1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1610" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1610"/>
+  <dimension ref="A1:I1611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43910,6 +43910,33 @@
       </c>
       <c r="I1610" t="inlineStr"/>
     </row>
+    <row r="1611">
+      <c r="A1611" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B1611" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C1611" t="n">
+        <v>4583.2998046875</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>4498.10009765625</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>4501.10009765625</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>229058</v>
+      </c>
+      <c r="G1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1611" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1611"/>
+  <dimension ref="A1:I1612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43937,6 +43937,33 @@
       </c>
       <c r="I1611" t="inlineStr"/>
     </row>
+    <row r="1612">
+      <c r="A1612" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B1612" t="n">
+        <v>4507.39990234375</v>
+      </c>
+      <c r="C1612" t="n">
+        <v>4561.2001953125</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>4431</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>4482.39990234375</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>188330</v>
+      </c>
+      <c r="G1612" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1612" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1612" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1612"/>
+  <dimension ref="A1:I1613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43964,6 +43964,33 @@
       </c>
       <c r="I1612" t="inlineStr"/>
     </row>
+    <row r="1613">
+      <c r="A1613" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B1613" t="n">
+        <v>4488</v>
+      </c>
+      <c r="C1613" t="n">
+        <v>4545.39990234375</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>4395.60009765625</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>4535.10009765625</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>136747</v>
+      </c>
+      <c r="G1613" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1613" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1613" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1613"/>
+  <dimension ref="A1:I1614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43991,6 +43991,33 @@
       </c>
       <c r="I1613" t="inlineStr"/>
     </row>
+    <row r="1614">
+      <c r="A1614" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B1614" t="n">
+        <v>4527.60009765625</v>
+      </c>
+      <c r="C1614" t="n">
+        <v>4627.10009765625</v>
+      </c>
+      <c r="D1614" t="n">
+        <v>4519.5</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>4590</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>114216</v>
+      </c>
+      <c r="G1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1614" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -44005,10 +44005,10 @@
         <v>4519.5</v>
       </c>
       <c r="E1614" t="n">
-        <v>4590</v>
+        <v>4593</v>
       </c>
       <c r="F1614" t="n">
-        <v>114216</v>
+        <v>124293</v>
       </c>
       <c r="G1614" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1614"/>
+  <dimension ref="A1:I1615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44018,6 +44018,33 @@
       </c>
       <c r="I1614" t="inlineStr"/>
     </row>
+    <row r="1615">
+      <c r="A1615" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B1615" t="n">
+        <v>4575.2001953125</v>
+      </c>
+      <c r="C1615" t="n">
+        <v>4577.2998046875</v>
+      </c>
+      <c r="D1615" t="n">
+        <v>4476</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>4516</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>109517</v>
+      </c>
+      <c r="G1615" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1615" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1615" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1615"/>
+  <dimension ref="A1:I1616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44045,6 +44045,33 @@
       </c>
       <c r="I1615" t="inlineStr"/>
     </row>
+    <row r="1616">
+      <c r="A1616" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B1616" t="n">
+        <v>4515.7998046875</v>
+      </c>
+      <c r="C1616" t="n">
+        <v>4571.2998046875</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>4492.2998046875</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>4515.7998046875</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>91793</v>
+      </c>
+      <c r="G1616" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1616" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1616" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1616"/>
+  <dimension ref="A1:I1617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44072,6 +44072,33 @@
       </c>
       <c r="I1616" t="inlineStr"/>
     </row>
+    <row r="1617">
+      <c r="A1617" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B1617" t="n">
+        <v>4520</v>
+      </c>
+      <c r="C1617" t="n">
+        <v>4525.10009765625</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>4454</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>4466.89990234375</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>95785</v>
+      </c>
+      <c r="G1617" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1617" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1617" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1617"/>
+  <dimension ref="A1:I1618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44099,6 +44099,33 @@
       </c>
       <c r="I1617" t="inlineStr"/>
     </row>
+    <row r="1618">
+      <c r="A1618" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B1618" t="n">
+        <v>4462.60009765625</v>
+      </c>
+      <c r="C1618" t="n">
+        <v>4543.2001953125</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>4450.10009765625</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>4503.2998046875</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>98778</v>
+      </c>
+      <c r="G1618" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1618" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1618" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1618"/>
+  <dimension ref="A1:I1619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44126,6 +44126,33 @@
       </c>
       <c r="I1618" t="inlineStr"/>
     </row>
+    <row r="1619">
+      <c r="A1619" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B1619" t="n">
+        <v>4503</v>
+      </c>
+      <c r="C1619" t="n">
+        <v>4508.7001953125</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>4347.5</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>4358</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>140612</v>
+      </c>
+      <c r="G1619" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1619" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1619" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -44137,13 +44137,13 @@
         <v>4508.7001953125</v>
       </c>
       <c r="D1619" t="n">
-        <v>4347.5</v>
+        <v>4336.60009765625</v>
       </c>
       <c r="E1619" t="n">
-        <v>4358</v>
+        <v>4365.2998046875</v>
       </c>
       <c r="F1619" t="n">
-        <v>140612</v>
+        <v>173440</v>
       </c>
       <c r="G1619" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1619"/>
+  <dimension ref="A1:I1620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44153,6 +44153,33 @@
       </c>
       <c r="I1619" t="inlineStr"/>
     </row>
+    <row r="1620">
+      <c r="A1620" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B1620" t="n">
+        <v>4354</v>
+      </c>
+      <c r="C1620" t="n">
+        <v>4377.5</v>
+      </c>
+      <c r="D1620" t="n">
+        <v>4293</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>4360.60009765625</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>125851</v>
+      </c>
+      <c r="G1620" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1620" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1620" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1620"/>
+  <dimension ref="A1:I1621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44180,6 +44180,33 @@
       </c>
       <c r="I1620" t="inlineStr"/>
     </row>
+    <row r="1621">
+      <c r="A1621" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B1621" t="n">
+        <v>4354.7001953125</v>
+      </c>
+      <c r="C1621" t="n">
+        <v>4388.60009765625</v>
+      </c>
+      <c r="D1621" t="n">
+        <v>4259.89990234375</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>4272.2998046875</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>112582</v>
+      </c>
+      <c r="G1621" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1621" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1621" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1621"/>
+  <dimension ref="A1:I1622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44207,6 +44207,33 @@
       </c>
       <c r="I1621" t="inlineStr"/>
     </row>
+    <row r="1622">
+      <c r="A1622" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B1622" t="n">
+        <v>4276.10009765625</v>
+      </c>
+      <c r="C1622" t="n">
+        <v>4281.10009765625</v>
+      </c>
+      <c r="D1622" t="n">
+        <v>4128</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>4132.10009765625</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>177584</v>
+      </c>
+      <c r="G1622" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1622" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1622" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1622"/>
+  <dimension ref="A1:I1623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44234,6 +44234,33 @@
       </c>
       <c r="I1622" t="inlineStr"/>
     </row>
+    <row r="1623">
+      <c r="A1623" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B1623" t="n">
+        <v>4094.39990234375</v>
+      </c>
+      <c r="C1623" t="n">
+        <v>4176.10009765625</v>
+      </c>
+      <c r="D1623" t="n">
+        <v>4046.199951171875</v>
+      </c>
+      <c r="E1623" t="n">
+        <v>4170</v>
+      </c>
+      <c r="F1623" t="n">
+        <v>161692</v>
+      </c>
+      <c r="G1623" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1623" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1623" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1623"/>
+  <dimension ref="A1:I1624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44261,6 +44261,33 @@
       </c>
       <c r="I1623" t="inlineStr"/>
     </row>
+    <row r="1624">
+      <c r="A1624" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B1624" t="n">
+        <v>4234.89990234375</v>
+      </c>
+      <c r="C1624" t="n">
+        <v>4267.7998046875</v>
+      </c>
+      <c r="D1624" t="n">
+        <v>4191.10009765625</v>
+      </c>
+      <c r="E1624" t="n">
+        <v>4240.2001953125</v>
+      </c>
+      <c r="F1624" t="n">
+        <v>117020</v>
+      </c>
+      <c r="G1624" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1624" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1624" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -44275,10 +44275,10 @@
         <v>4191.10009765625</v>
       </c>
       <c r="E1624" t="n">
-        <v>4240.2001953125</v>
+        <v>4238.7998046875</v>
       </c>
       <c r="F1624" t="n">
-        <v>117020</v>
+        <v>132801</v>
       </c>
       <c r="G1624" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1624"/>
+  <dimension ref="A1:I1625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44288,6 +44288,33 @@
       </c>
       <c r="I1624" t="inlineStr"/>
     </row>
+    <row r="1625">
+      <c r="A1625" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B1625" t="n">
+        <v>4289.39990234375</v>
+      </c>
+      <c r="C1625" t="n">
+        <v>4391.5</v>
+      </c>
+      <c r="D1625" t="n">
+        <v>4283.39990234375</v>
+      </c>
+      <c r="E1625" t="n">
+        <v>4346.5</v>
+      </c>
+      <c r="F1625" t="n">
+        <v>121910</v>
+      </c>
+      <c r="G1625" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1625" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1625" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1625"/>
+  <dimension ref="A1:I1626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44315,6 +44315,33 @@
       </c>
       <c r="I1625" t="inlineStr"/>
     </row>
+    <row r="1626">
+      <c r="A1626" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B1626" t="n">
+        <v>4331.2998046875</v>
+      </c>
+      <c r="C1626" t="n">
+        <v>4376.5</v>
+      </c>
+      <c r="D1626" t="n">
+        <v>4326.7001953125</v>
+      </c>
+      <c r="E1626" t="n">
+        <v>4363.10009765625</v>
+      </c>
+      <c r="F1626" t="n">
+        <v>83293</v>
+      </c>
+      <c r="G1626" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1626" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1626" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1626"/>
+  <dimension ref="A1:I1627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44342,6 +44342,33 @@
       </c>
       <c r="I1626" t="inlineStr"/>
     </row>
+    <row r="1627">
+      <c r="A1627" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B1627" t="n">
+        <v>4352.60009765625</v>
+      </c>
+      <c r="C1627" t="n">
+        <v>4386.7001953125</v>
+      </c>
+      <c r="D1627" t="n">
+        <v>4335.60009765625</v>
+      </c>
+      <c r="E1627" t="n">
+        <v>4379.7001953125</v>
+      </c>
+      <c r="F1627" t="n">
+        <v>69738</v>
+      </c>
+      <c r="G1627" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1627" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1627" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1627"/>
+  <dimension ref="A1:I1628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44369,6 +44369,33 @@
       </c>
       <c r="I1627" t="inlineStr"/>
     </row>
+    <row r="1628">
+      <c r="A1628" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B1628" t="n">
+        <v>4275.10009765625</v>
+      </c>
+      <c r="C1628" t="n">
+        <v>4350.2001953125</v>
+      </c>
+      <c r="D1628" t="n">
+        <v>4233</v>
+      </c>
+      <c r="E1628" t="n">
+        <v>4245.39990234375</v>
+      </c>
+      <c r="F1628" t="n">
+        <v>122984</v>
+      </c>
+      <c r="G1628" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1628" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1628" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1628"/>
+  <dimension ref="A1:I1629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44396,6 +44396,33 @@
       </c>
       <c r="I1628" t="inlineStr"/>
     </row>
+    <row r="1629">
+      <c r="A1629" s="1" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B1629" t="n">
+        <v>4231.2001953125</v>
+      </c>
+      <c r="C1629" t="n">
+        <v>4231.39990234375</v>
+      </c>
+      <c r="D1629" t="n">
+        <v>4138.7001953125</v>
+      </c>
+      <c r="E1629" t="n">
+        <v>4170.89990234375</v>
+      </c>
+      <c r="F1629" t="n">
+        <v>72208</v>
+      </c>
+      <c r="G1629" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1629" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1629" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -44410,10 +44410,10 @@
         <v>4138.7001953125</v>
       </c>
       <c r="E1629" t="n">
-        <v>4170.89990234375</v>
+        <v>4172.89990234375</v>
       </c>
       <c r="F1629" t="n">
-        <v>72208</v>
+        <v>73110</v>
       </c>
       <c r="G1629" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1629"/>
+  <dimension ref="A1:I1630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44423,6 +44423,33 @@
       </c>
       <c r="I1629" t="inlineStr"/>
     </row>
+    <row r="1630">
+      <c r="A1630" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B1630" t="n">
+        <v>4163.89990234375</v>
+      </c>
+      <c r="C1630" t="n">
+        <v>4238.10009765625</v>
+      </c>
+      <c r="D1630" t="n">
+        <v>4138.7001953125</v>
+      </c>
+      <c r="E1630" t="n">
+        <v>4207.5</v>
+      </c>
+      <c r="F1630" t="n">
+        <v>169542</v>
+      </c>
+      <c r="G1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1630" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1630"/>
+  <dimension ref="A1:I1631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44450,6 +44450,33 @@
       </c>
       <c r="I1630" t="inlineStr"/>
     </row>
+    <row r="1631">
+      <c r="A1631" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B1631" t="n">
+        <v>4210.7998046875</v>
+      </c>
+      <c r="C1631" t="n">
+        <v>4216</v>
+      </c>
+      <c r="D1631" t="n">
+        <v>4108.2001953125</v>
+      </c>
+      <c r="E1631" t="n">
+        <v>4157.5</v>
+      </c>
+      <c r="F1631" t="n">
+        <v>101441</v>
+      </c>
+      <c r="G1631" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1631" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1631" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1631"/>
+  <dimension ref="A1:I1632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44477,6 +44477,33 @@
       </c>
       <c r="I1631" t="inlineStr"/>
     </row>
+    <row r="1632">
+      <c r="A1632" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B1632" t="n">
+        <v>4130</v>
+      </c>
+      <c r="C1632" t="n">
+        <v>4132.39990234375</v>
+      </c>
+      <c r="D1632" t="n">
+        <v>3980.300048828125</v>
+      </c>
+      <c r="E1632" t="n">
+        <v>4030.5</v>
+      </c>
+      <c r="F1632" t="n">
+        <v>149944</v>
+      </c>
+      <c r="G1632" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1632" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1632" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1632"/>
+  <dimension ref="A1:I1633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44504,6 +44504,33 @@
       </c>
       <c r="I1632" t="inlineStr"/>
     </row>
+    <row r="1633">
+      <c r="A1633" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B1633" t="n">
+        <v>4019</v>
+      </c>
+      <c r="C1633" t="n">
+        <v>4060</v>
+      </c>
+      <c r="D1633" t="n">
+        <v>3976.300048828125</v>
+      </c>
+      <c r="E1633" t="n">
+        <v>4055.199951171875</v>
+      </c>
+      <c r="F1633" t="n">
+        <v>121410</v>
+      </c>
+      <c r="G1633" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1633" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1633" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1633"/>
+  <dimension ref="A1:I1634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44531,6 +44531,33 @@
       </c>
       <c r="I1633" t="inlineStr"/>
     </row>
+    <row r="1634">
+      <c r="A1634" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B1634" t="n">
+        <v>4044.39990234375</v>
+      </c>
+      <c r="C1634" t="n">
+        <v>4111.5</v>
+      </c>
+      <c r="D1634" t="n">
+        <v>3998.10009765625</v>
+      </c>
+      <c r="E1634" t="n">
+        <v>4100.60009765625</v>
+      </c>
+      <c r="F1634" t="n">
+        <v>96987</v>
+      </c>
+      <c r="G1634" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1634" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1634" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -44545,10 +44545,10 @@
         <v>3998.10009765625</v>
       </c>
       <c r="E1634" t="n">
-        <v>4100.60009765625</v>
+        <v>4096.2998046875</v>
       </c>
       <c r="F1634" t="n">
-        <v>96987</v>
+        <v>114770</v>
       </c>
       <c r="G1634" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1634"/>
+  <dimension ref="A1:I1635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44558,6 +44558,33 @@
       </c>
       <c r="I1634" t="inlineStr"/>
     </row>
+    <row r="1635">
+      <c r="A1635" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B1635" t="n">
+        <v>4101.10009765625</v>
+      </c>
+      <c r="C1635" t="n">
+        <v>4102.89990234375</v>
+      </c>
+      <c r="D1635" t="n">
+        <v>4012</v>
+      </c>
+      <c r="E1635" t="n">
+        <v>4042.60009765625</v>
+      </c>
+      <c r="F1635" t="n">
+        <v>91156</v>
+      </c>
+      <c r="G1635" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1635" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1635" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1635"/>
+  <dimension ref="A1:I1636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44585,6 +44585,33 @@
       </c>
       <c r="I1635" t="inlineStr"/>
     </row>
+    <row r="1636">
+      <c r="A1636" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B1636" t="n">
+        <v>4032.5</v>
+      </c>
+      <c r="C1636" t="n">
+        <v>4078.10009765625</v>
+      </c>
+      <c r="D1636" t="n">
+        <v>3955.39990234375</v>
+      </c>
+      <c r="E1636" t="n">
+        <v>4044.199951171875</v>
+      </c>
+      <c r="F1636" t="n">
+        <v>107591</v>
+      </c>
+      <c r="G1636" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1636" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1636" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1636"/>
+  <dimension ref="A1:I1637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44612,6 +44612,33 @@
       </c>
       <c r="I1636" t="inlineStr"/>
     </row>
+    <row r="1637">
+      <c r="A1637" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B1637" t="n">
+        <v>4025</v>
+      </c>
+      <c r="C1637" t="n">
+        <v>4131</v>
+      </c>
+      <c r="D1637" t="n">
+        <v>3973</v>
+      </c>
+      <c r="E1637" t="n">
+        <v>4093.10009765625</v>
+      </c>
+      <c r="F1637" t="n">
+        <v>121181</v>
+      </c>
+      <c r="G1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1637" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1637"/>
+  <dimension ref="A1:I1638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44639,6 +44639,33 @@
       </c>
       <c r="I1637" t="inlineStr"/>
     </row>
+    <row r="1638">
+      <c r="A1638" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B1638" t="n">
+        <v>4049.199951171875</v>
+      </c>
+      <c r="C1638" t="n">
+        <v>4157.10009765625</v>
+      </c>
+      <c r="D1638" t="n">
+        <v>4042.800048828125</v>
+      </c>
+      <c r="E1638" t="n">
+        <v>4138.10009765625</v>
+      </c>
+      <c r="F1638" t="n">
+        <v>102915</v>
+      </c>
+      <c r="G1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1638" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1638"/>
+  <dimension ref="A1:I1639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44666,6 +44666,33 @@
       </c>
       <c r="I1638" t="inlineStr"/>
     </row>
+    <row r="1639">
+      <c r="A1639" s="1" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B1639" t="n">
+        <v>4138</v>
+      </c>
+      <c r="C1639" t="n">
+        <v>4208.2998046875</v>
+      </c>
+      <c r="D1639" t="n">
+        <v>4133.7998046875</v>
+      </c>
+      <c r="E1639" t="n">
+        <v>4177.2998046875</v>
+      </c>
+      <c r="F1639" t="n">
+        <v>52381</v>
+      </c>
+      <c r="G1639" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1639" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1639" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -44680,10 +44680,10 @@
         <v>4133.7998046875</v>
       </c>
       <c r="E1639" t="n">
-        <v>4177.2998046875</v>
+        <v>4187.2998046875</v>
       </c>
       <c r="F1639" t="n">
-        <v>52381</v>
+        <v>54673</v>
       </c>
       <c r="G1639" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1639"/>
+  <dimension ref="A1:I1640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44693,6 +44693,33 @@
       </c>
       <c r="I1639" t="inlineStr"/>
     </row>
+    <row r="1640">
+      <c r="A1640" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B1640" t="n">
+        <v>4187.5</v>
+      </c>
+      <c r="C1640" t="n">
+        <v>4215.5</v>
+      </c>
+      <c r="D1640" t="n">
+        <v>4133.7998046875</v>
+      </c>
+      <c r="E1640" t="n">
+        <v>4165.39990234375</v>
+      </c>
+      <c r="F1640" t="n">
+        <v>132422</v>
+      </c>
+      <c r="G1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1640" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1640"/>
+  <dimension ref="A1:I1641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44720,6 +44720,33 @@
       </c>
       <c r="I1640" t="inlineStr"/>
     </row>
+    <row r="1641">
+      <c r="A1641" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B1641" t="n">
+        <v>4176.39990234375</v>
+      </c>
+      <c r="C1641" t="n">
+        <v>4192.39990234375</v>
+      </c>
+      <c r="D1641" t="n">
+        <v>4127.7001953125</v>
+      </c>
+      <c r="E1641" t="n">
+        <v>4154.39990234375</v>
+      </c>
+      <c r="F1641" t="n">
+        <v>82917</v>
+      </c>
+      <c r="G1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1641" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1641"/>
+  <dimension ref="A1:I1642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44747,6 +44747,33 @@
       </c>
       <c r="I1641" t="inlineStr"/>
     </row>
+    <row r="1642">
+      <c r="A1642" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B1642" t="n">
+        <v>4106.5</v>
+      </c>
+      <c r="C1642" t="n">
+        <v>4144.7001953125</v>
+      </c>
+      <c r="D1642" t="n">
+        <v>4032.5</v>
+      </c>
+      <c r="E1642" t="n">
+        <v>4046.89990234375</v>
+      </c>
+      <c r="F1642" t="n">
+        <v>128512</v>
+      </c>
+      <c r="G1642" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1642" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1642" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1642"/>
+  <dimension ref="A1:I1643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44774,6 +44774,33 @@
       </c>
       <c r="I1642" t="inlineStr"/>
     </row>
+    <row r="1643">
+      <c r="A1643" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B1643" t="n">
+        <v>4087.60009765625</v>
+      </c>
+      <c r="C1643" t="n">
+        <v>4148.39990234375</v>
+      </c>
+      <c r="D1643" t="n">
+        <v>4063.39990234375</v>
+      </c>
+      <c r="E1643" t="n">
+        <v>4142</v>
+      </c>
+      <c r="F1643" t="n">
+        <v>93458</v>
+      </c>
+      <c r="G1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1643" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1643"/>
+  <dimension ref="A1:I1644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44801,6 +44801,33 @@
       </c>
       <c r="I1643" t="inlineStr"/>
     </row>
+    <row r="1644">
+      <c r="A1644" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B1644" t="n">
+        <v>4135.39990234375</v>
+      </c>
+      <c r="C1644" t="n">
+        <v>4144.60009765625</v>
+      </c>
+      <c r="D1644" t="n">
+        <v>4081.699951171875</v>
+      </c>
+      <c r="E1644" t="n">
+        <v>4122.39990234375</v>
+      </c>
+      <c r="F1644" t="n">
+        <v>75580</v>
+      </c>
+      <c r="G1644" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1644" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1644" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -44815,10 +44815,10 @@
         <v>4081.699951171875</v>
       </c>
       <c r="E1644" t="n">
-        <v>4122.39990234375</v>
+        <v>4113.7001953125</v>
       </c>
       <c r="F1644" t="n">
-        <v>75580</v>
+        <v>91801</v>
       </c>
       <c r="G1644" t="n">
         <v>0</v>

--- a/data/gold_data.xlsx
+++ b/data/gold_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1644"/>
+  <dimension ref="A1:I1645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44828,6 +44828,33 @@
       </c>
       <c r="I1644" t="inlineStr"/>
     </row>
+    <row r="1645">
+      <c r="A1645" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1645" t="n">
+        <v>4163.89990234375</v>
+      </c>
+      <c r="C1645" t="n">
+        <v>4170.7001953125</v>
+      </c>
+      <c r="D1645" t="n">
+        <v>4076.39990234375</v>
+      </c>
+      <c r="E1645" t="n">
+        <v>4107</v>
+      </c>
+      <c r="F1645" t="n">
+        <v>106211</v>
+      </c>
+      <c r="G1645" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1645" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1645" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
